--- a/docs/Mau_03_Bo_bieu_mau_Kiem_thu.xlsx
+++ b/docs/Mau_03_Bo_bieu_mau_Kiem_thu.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>Sinh viên A - SV20260001</t>
+          <t>Lại Thị Thanh Xuân – 23110309</t>
         </is>
       </c>
       <c r="C7" s="22" t="n"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8001</t>
+          <t>https://itick-platform.onrender.com/ (Local: http://127.0.0.1:8001)</t>
         </is>
       </c>
       <c r="C8" s="22" t="n"/>
@@ -709,6 +709,18 @@
       </c>
       <c r="C10" s="22" t="n"/>
       <c r="D10" s="22" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Thư mục Drive tài liệu &amp; Bug</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1K9Mq0RubxVY5YOycdWN-DqwUO4dmS-kc?usp=sharing</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="17">
       <c r="A12" s="23" t="inlineStr">
@@ -1490,7 +1502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M499"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.1" customWidth="1" style="16" min="1" max="2"/>
@@ -3424,1856 +3436,1856 @@
       <c r="M35" s="24" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>TC-FR07-003</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>FR-07</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>Giá trị biên (BVA)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Áp dụng voucher GIAM20 cho đơn hàng lớn vượt trần 150k</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>Đơn hàng trị giá 2.000.000đ</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>Voucher GIAM20 (giảm 20%, trần 150k)</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="16" t="inlineStr">
         <is>
           <t>1. Nhập GIAM20 cho đơn 2.000.000đ
 2. Bấm Áp dụng</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="16" t="inlineStr">
         <is>
           <t>Mức giảm bị chặn ở trần tối đa 150.000đ, thành tiền 1.850.000đ</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="16" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="16" t="inlineStr">
         <is>
           <t>Giảm 400.000đ (20%), vượt trần tối đa 150.000đ theo quy định</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" s="16" t="inlineStr">
         <is>
           <t>BUG-002</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" s="16" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>TC-FR07-004</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>FR-07</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>Bảng quyết định</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>Nhập mã voucher sai hoặc đã hết hạn</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>Đang đặt vé</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>Voucher 'VOUCHEREXPIRED'</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="16" t="inlineStr">
         <is>
           <t>1. Nhập mã voucher sai
 2. Bấm Áp dụng</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="16" t="inlineStr">
         <is>
           <t>Báo lỗi: 'Mã giảm giá không tồn tại hoặc đã hết hạn sử dụng'</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="16" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="16" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="16" t="inlineStr">
         <is>
           <t>Hiển thị thông báo nhầm lẫn: 'Mật khẩu tài khoản không đúng, vui lòng thử lại'</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" s="16" t="inlineStr">
         <is>
           <t>BUG-010</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" s="16" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>TC-FR07-005</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>FR-07</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>Bảng quyết định</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Áp dụng voucher khi đơn hàng chưa đạt giá trị tối thiểu</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>Đơn hàng 100.000đ</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>Voucher yêu cầu đơn tối thiểu 200.000đ</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>1. Nhập mã voucher
 2. Bấm Áp dụng</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="16" t="inlineStr">
         <is>
           <t>Báo lỗi: Đơn hàng chưa đạt giá trị tối thiểu để áp dụng mã này</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="K38" s="16" t="inlineStr"/>
+      <c r="L38" s="16" t="inlineStr"/>
+      <c r="M38" s="16" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-001</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>FR-08</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>Bảng quyết định</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>Thanh toán bằng ví nội bộ khi số dư đủ tiền</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>Số dư ví 1.000.000đ, đơn hàng 400.000đ</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="16" t="inlineStr">
         <is>
           <t>Phương thức: WALLET</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="16" t="inlineStr">
         <is>
           <t>1. Chọn Thanh toán ví
 2. Bấm Xác nhận thanh toán</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="16" t="inlineStr">
         <is>
           <t>Trừ ví 400.000đ, số dư còn 600.000đ, xuất vé điện tử thành công</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="K39" s="16" t="inlineStr"/>
+      <c r="L39" s="16" t="inlineStr"/>
+      <c r="M39" s="16" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-002</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>FR-08</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>Bảng quyết định</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Thanh toán bằng ví khi số dư không đủ tiền</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>Số dư ví 100.000đ, đơn hàng 500.000đ</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>Phương thức: WALLET</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>1. Chọn Thanh toán ví
 2. Bấm Xác nhận</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="16" t="inlineStr">
         <is>
           <t>Báo lỗi: Số dư ví không đủ, gợi ý nạp thêm tiền hoặc chọn VietQR</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="K40" s="16" t="inlineStr"/>
+      <c r="L40" s="16" t="inlineStr"/>
+      <c r="M40" s="16" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-003</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>FR-08</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="16" t="inlineStr">
         <is>
           <t>Chuyển trạng thái</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>Tạo yêu cầu thanh toán qua cổng VietQR PayOS</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>Đơn hàng 500.000đ</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="16" t="inlineStr">
         <is>
           <t>Phương thức: PAYOS</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="16" t="inlineStr">
         <is>
           <t>1. Chọn VietQR PayOS
 2. Bấm Tạo thanh toán</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="16" t="inlineStr">
         <is>
           <t>Hiển thị mã QR PayOS và thông tin chuyển khoản chính xác</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="K41" s="16" t="inlineStr"/>
+      <c r="L41" s="16" t="inlineStr"/>
+      <c r="M41" s="16" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-004</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>FR-08</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="16" t="inlineStr">
         <is>
           <t>Error guessing / Checklist</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra định dạng hiển thị tiền tệ tổng thực thu</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="16" t="inlineStr">
         <is>
           <t>Đơn hàng 1.000.000đ</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="16" t="inlineStr">
         <is>
           <t>Màn hình tóm tắt thanh toán</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="16" t="inlineStr">
         <is>
           <t>1. Quan sát dòng Tổng thực thu trên giao diện</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="16" t="inlineStr">
         <is>
           <t>Hiển thị '1,000,000 đ' có dấu phẩy phân cách hàng nghìn và căn lề phải</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" s="16" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="16" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="16" t="inlineStr">
         <is>
           <t>Hiển thị '1000000 VND' không dấu phẩy và bị căn trái lệch cột</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L42" s="16" t="inlineStr">
         <is>
           <t>BUG-008</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" s="16" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>TC-FR09-001</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>FR-09</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr">
         <is>
           <t>Giá trị biên (BVA)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>Hủy vé trước khi sự kiện diễn ra &gt; 48 giờ</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="16" t="inlineStr">
         <is>
           <t>Vé hợp lệ, sự kiện diễn ra sau 72 giờ</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="16" t="inlineStr">
         <is>
           <t>Ticket ID hợp lệ</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="16" t="inlineStr">
         <is>
           <t>1. Mở chi tiết vé
 2. Bấm Hủy vé</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="16" t="inlineStr">
         <is>
           <t>Hủy vé thành công, hoàn lại 90% giá vé vào ví khách</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="K43" s="16" t="inlineStr"/>
+      <c r="L43" s="16" t="inlineStr"/>
+      <c r="M43" s="16" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>TC-FR09-002</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>FR-09</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>Giá trị biên (BVA)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>Hủy vé trước khi sự kiện diễn ra từ 24 đến 48 giờ</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="16" t="inlineStr">
         <is>
           <t>Vé hợp lệ, sự kiện diễn ra sau 30 giờ</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="16" t="inlineStr">
         <is>
           <t>Ticket ID hợp lệ</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="16" t="inlineStr">
         <is>
           <t>1. Bấm Hủy vé</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="16" t="inlineStr">
         <is>
           <t>Hủy vé thành công, hoàn lại 70% giá vé vào ví khách</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="K44" s="16" t="inlineStr"/>
+      <c r="L44" s="16" t="inlineStr"/>
+      <c r="M44" s="16" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>TC-FR09-003</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>FR-09</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>Giá trị biên (BVA)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>Hủy vé sát giờ diễn ra sự kiện &lt; 24 giờ</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="16" t="inlineStr">
         <is>
           <t>Vé hợp lệ, sự kiện diễn ra sau 5 giờ</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="16" t="inlineStr">
         <is>
           <t>Ticket ID hợp lệ</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="16" t="inlineStr">
         <is>
           <t>1. Gửi request POST /api/bookings/{ticket_id}/cancel</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="16" t="inlineStr">
         <is>
           <t>Từ chối hủy vé theo quy định: Không được hủy vé trước sự kiện dưới 24h</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="16" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="16" t="inlineStr">
         <is>
           <t>Hệ thống vẫn chấp nhận hủy vé và hoàn lại tiền vào ví</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L45" s="16" t="inlineStr">
         <is>
           <t>BUG-003</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" s="16" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>TC-FR09-004</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>FR-09</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>Chuyển trạng thái</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>Thử hủy vé đã qua cổng soát vé (CHECKED_IN)</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="16" t="inlineStr">
         <is>
           <t>Vé có status == CHECKED_IN</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="16" t="inlineStr">
         <is>
           <t>Ticket ID đã check-in</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="16" t="inlineStr">
         <is>
           <t>1. Gửi yêu cầu hủy vé đã check-in</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="16" t="inlineStr">
         <is>
           <t>Từ chối: Vé đã sử dụng vào cổng không được phép hủy</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="K46" s="16" t="inlineStr"/>
+      <c r="L46" s="16" t="inlineStr"/>
+      <c r="M46" s="16" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>TC-FR09-005</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>FR-09</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>Chuyển trạng thái</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>Thử hủy lại một vé đã ở trạng thái CANCELLED</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="16" t="inlineStr">
         <is>
           <t>Vé có status == CANCELLED</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="16" t="inlineStr">
         <is>
           <t>Ticket ID đã hủy trước đó</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="16" t="inlineStr">
         <is>
           <t>1. Gửi yêu cầu hủy vé lần 2</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="16" t="inlineStr">
         <is>
           <t>Từ chối: Vé đã được hủy trước đó, không thể hủy lặp lại</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="K47" s="16" t="inlineStr"/>
+      <c r="L47" s="16" t="inlineStr"/>
+      <c r="M47" s="16" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>TC-FR10-001</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>FR-10</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="16" t="inlineStr">
         <is>
           <t>Phân hoạch tương đương (EP)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>Ban tổ chức xem danh sách người tham gia theo sự kiện</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="16" t="inlineStr">
         <is>
           <t>Đã đăng nhập vai Ban tổ chức sở hữu sự kiện</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="16" t="inlineStr">
         <is>
           <t>Event ID 1</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="16" t="inlineStr">
         <is>
           <t>1. Mở trang Quản lý sự kiện
 2. Chọn tab Người tham gia</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="16" t="inlineStr">
         <is>
           <t>Hiển thị bảng danh sách đầy đủ thông tin khách, mã vé, trạng thái</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="K48" s="16" t="inlineStr"/>
+      <c r="L48" s="16" t="inlineStr"/>
+      <c r="M48" s="16" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>TC-FR10-002</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>FR-10</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>Phân hoạch tương đương (EP)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>Lọc danh sách người tham gia theo trạng thái vé</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="16" t="inlineStr">
         <is>
           <t>Sự kiện có khách ở nhiều trạng thái</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="16" t="inlineStr">
         <is>
           <t>Filter status: CHECKED_IN</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="16" t="inlineStr">
         <is>
           <t>1. Chọn bộ lọc 'Đã tham dự'
 2. Quan sát bảng</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="16" t="inlineStr">
         <is>
           <t>Chỉ hiển thị các khách hàng có vé đã check-in thành công</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="K49" s="16" t="inlineStr"/>
+      <c r="L49" s="16" t="inlineStr"/>
+      <c r="M49" s="16" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>TC-FR10-003</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>FR-10</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>Phân hoạch tương đương (EP)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>Xuất file Excel danh sách người tham gia sự kiện</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="16" t="inlineStr">
         <is>
           <t>Sự kiện có danh sách khách đăng ký</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="16" t="inlineStr">
         <is>
           <t>Bấm nút Xuất Excel</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="16" t="inlineStr">
         <is>
           <t>1. Mở tab Người tham gia
 2. Bấm nút 'Xuất Excel Soát Vé'</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="16" t="inlineStr">
         <is>
           <t>Tải về file Excel .xlsx chuẩn định dạng, đầy đủ các cột thông tin</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="K50" s="16" t="inlineStr"/>
+      <c r="L50" s="16" t="inlineStr"/>
+      <c r="M50" s="16" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>TC-FR10-004</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>FR-10</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="16" t="inlineStr">
         <is>
           <t>Error guessing / Checklist</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra tính năng dropdown chọn trạng thái trong Excel</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="16" t="inlineStr">
         <is>
           <t>Đã tải file Excel soát vé về máy</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="16" t="inlineStr">
         <is>
           <t>Mở file Excel</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="16" t="inlineStr">
         <is>
           <t>1. Mở file Excel
 2. Nhấp vào ô tại cột Trạng thái soát vé</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="16" t="inlineStr">
         <is>
           <t>Hiển thị dropdown danh sách lựa chọn: 'Đã tham dự', 'Chưa check-in', 'Vắng mặt', 'Đã hủy vé'</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="K51" s="16" t="inlineStr"/>
+      <c r="L51" s="16" t="inlineStr"/>
+      <c r="M51" s="16" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>TC-FR11-001</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>FR-11</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="16" t="inlineStr">
         <is>
           <t>Chuyển trạng thái</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>Admin phê duyệt sự kiện từ PENDING sang PUBLISHED</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="16" t="inlineStr">
         <is>
           <t>Đã đăng nhập vai Admin</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="16" t="inlineStr">
         <is>
           <t>Event ID ở trạng thái PENDING</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="16" t="inlineStr">
         <is>
           <t>1. Mở /admin/events
 2. Bấm Duyệt sự kiện</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="16" t="inlineStr">
         <is>
           <t>Sự kiện chuyển sang PUBLISHED, hiển thị công khai trên trang chủ</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="K52" s="16" t="inlineStr"/>
+      <c r="L52" s="16" t="inlineStr"/>
+      <c r="M52" s="16" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>TC-FR11-002</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>FR-11</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="16" t="inlineStr">
         <is>
           <t>Chuyển trạng thái</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>Admin từ chối sự kiện không đạt tiêu chuẩn</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="16" t="inlineStr">
         <is>
           <t>Đã đăng nhập vai Admin</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="16" t="inlineStr">
         <is>
           <t>Event ID ở trạng thái PENDING</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="16" t="inlineStr">
         <is>
           <t>1. Mở danh sách duyệt sự kiện
 2. Bấm Từ chối</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="16" t="inlineStr">
         <is>
           <t>Sự kiện chuyển sang REJECTED, không xuất hiện trên trang chủ</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
+      <c r="K53" s="16" t="inlineStr"/>
+      <c r="L53" s="16" t="inlineStr"/>
+      <c r="M53" s="16" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>TC-FR11-003</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>FR-11</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="16" t="inlineStr">
         <is>
           <t>Phân hoạch tương đương (EP)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>Admin cập nhật tỷ lệ phí sàn hệ thống</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="16" t="inlineStr">
         <is>
           <t>Đã đăng nhập vai Admin</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="16" t="inlineStr">
         <is>
           <t>platform_fee_percent = 6.0</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="16" t="inlineStr">
         <is>
           <t>1. Gửi PUT /api/admin/system/fee
 2. Truy vấn lại</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="16" t="inlineStr">
         <is>
           <t>Cập nhật thành công, phí sàn mới được áp dụng cho các đơn sau</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J54" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="K54" s="16" t="inlineStr"/>
+      <c r="L54" s="16" t="inlineStr"/>
+      <c r="M54" s="16" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>TC-FR11-004</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>FR-11</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="16" t="inlineStr">
         <is>
           <t>Phân quyền</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>Người dùng vai Khách cố tình gọi API Quản trị Admin</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="16" t="inlineStr">
         <is>
           <t>Đã đăng nhập vai Khách Attendee</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="16" t="inlineStr">
         <is>
           <t>GET /api/admin/users</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="16" t="inlineStr">
         <is>
           <t>1. Dùng token Attendee gọi GET /api/admin/users</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="16" t="inlineStr">
         <is>
           <t>Bị chặn với mã lỗi HTTP 403 Forbidden: Quyền truy cập bị từ chối</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J55" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+      <c r="K55" s="16" t="inlineStr"/>
+      <c r="L55" s="16" t="inlineStr"/>
+      <c r="M55" s="16" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="16" t="inlineStr">
         <is>
           <t>TC-FR11-005</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="16" t="inlineStr">
         <is>
           <t>FR-11</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="16" t="inlineStr">
         <is>
           <t>Phân quyền</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>Ban tổ chức cố tình truy cập đơn hàng của sự kiện khác</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="16" t="inlineStr">
         <is>
           <t>Đã đăng nhập Ban tổ chức A</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="16" t="inlineStr">
         <is>
           <t>Xem đơn hàng của Ban tổ chức B</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="16" t="inlineStr">
         <is>
           <t>1. Gửi request xem đơn hàng của BTC B</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="16" t="inlineStr">
         <is>
           <t>Bị chặn với HTTP 403 Forbidden</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J56" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="K56" s="16" t="inlineStr"/>
+      <c r="L56" s="16" t="inlineStr"/>
+      <c r="M56" s="16" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="16" t="inlineStr">
         <is>
           <t>TC-FR12-001</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="16" t="inlineStr">
         <is>
           <t>FR-12</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="16" t="inlineStr">
         <is>
           <t>Chuyển trạng thái</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>Soát vé hợp lệ trạng thái ISSUED lần đầu</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="16" t="inlineStr">
         <is>
           <t>Đã đăng nhập nhân viên soát vé</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="16" t="inlineStr">
         <is>
           <t>Mã vé TICK-2026-VALID01</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="16" t="inlineStr">
         <is>
           <t>1. Nhập mã vé hợp lệ
 2. Bấm Xác nhận Check-in</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="16" t="inlineStr">
         <is>
           <t>Xác thực thành công, vé chuyển sang CHECKED_IN, lưu giờ vào cổng</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J57" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="K57" s="16" t="inlineStr"/>
+      <c r="L57" s="16" t="inlineStr"/>
+      <c r="M57" s="16" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="16" t="inlineStr">
         <is>
           <t>TC-FR12-002</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="16" t="inlineStr">
         <is>
           <t>FR-12</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="16" t="inlineStr">
         <is>
           <t>Chuyển trạng thái</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>Quét lại vé đã check-in thành công lần thứ 2</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="16" t="inlineStr">
         <is>
           <t>Vé đã có status == CHECKED_IN</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="16" t="inlineStr">
         <is>
           <t>Mã vé đã quét trước đó</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="16" t="inlineStr">
         <is>
           <t>1. Nhập lại mã vé đã check-in
 2. Bấm Check-in</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="16" t="inlineStr">
         <is>
           <t>Báo cảnh báo màu vàng: 'Vé đã được check-in lúc HH:mm:ss', từ chối</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="K58" s="16" t="inlineStr"/>
+      <c r="L58" s="16" t="inlineStr"/>
+      <c r="M58" s="16" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>TC-FR12-003</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="16" t="inlineStr">
         <is>
           <t>FR-12</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="16" t="inlineStr">
         <is>
           <t>Bảng quyết định</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="16" t="inlineStr">
         <is>
           <t>Quét mã vé giả mạo không tồn tại trên hệ thống</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="16" t="inlineStr">
         <is>
           <t>Đang ở cổng soát vé</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="16" t="inlineStr">
         <is>
           <t>Mã vé 'FAKE-TICKET-999'</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="16" t="inlineStr">
         <is>
           <t>1. Nhập mã vé giả
 2. Bấm Check-in</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" s="16" t="inlineStr">
         <is>
           <t>Báo lỗi đỏ: 'Mã vé không hợp lệ hoặc không tồn tại'</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J59" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="K59" s="16" t="inlineStr"/>
+      <c r="L59" s="16" t="inlineStr"/>
+      <c r="M59" s="16" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="16" t="inlineStr">
         <is>
           <t>TC-FR12-004</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="16" t="inlineStr">
         <is>
           <t>FR-12</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="16" t="inlineStr">
         <is>
           <t>Chuyển trạng thái</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>Quét mã vé đã bị hủy (status == CANCELLED)</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="16" t="inlineStr">
         <is>
           <t>Vé TICK-2026-CANCEL03 đã hủy</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="16" t="inlineStr">
         <is>
           <t>Mã vé đã bị hủy</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="16" t="inlineStr">
         <is>
           <t>1. Nhập mã vé đã bị hủy
 2. Bấm Check-in</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="16" t="inlineStr">
         <is>
           <t>Từ chối check-in, báo lỗi đỏ: 'Vé đã bị hủy và hoàn tiền'</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J60" s="16" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K60" s="16" t="inlineStr">
         <is>
           <t>Hệ thống vẫn chuyển trạng thái sang CHECKED_IN và báo hợp lệ</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L60" s="16" t="inlineStr">
         <is>
           <t>BUG-005</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
+      <c r="M60" s="16" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="16" t="inlineStr">
         <is>
           <t>TC-FR13-001</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="16" t="inlineStr">
         <is>
           <t>FR-13</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="16" t="inlineStr">
         <is>
           <t>Bảng quyết định</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="16" t="inlineStr">
         <is>
           <t>Tính toán doanh thu thực nhận sau khi khấu trừ 5% phí sàn</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="16" t="inlineStr">
         <is>
           <t>Sự kiện bán được tổng tiền vé 10.000.000đ</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="16" t="inlineStr">
         <is>
           <t>Event ID 1</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="16" t="inlineStr">
         <is>
           <t>1. Mở trang Báo cáo doanh thu
 2. Kiểm tra số tiền</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="16" t="inlineStr">
         <is>
           <t>Doanh thu hiển thị 9.500.000đ (khấu trừ đúng 5% = 500.000đ phí sàn)</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J61" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
+      <c r="K61" s="16" t="inlineStr"/>
+      <c r="L61" s="16" t="inlineStr"/>
+      <c r="M61" s="16" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>TC-FR13-002</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="16" t="inlineStr">
         <is>
           <t>FR-13</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="16" t="inlineStr">
         <is>
           <t>Phân hoạch tương đương (EP)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="16" t="inlineStr">
         <is>
           <t>Xem biểu đồ số lượng vé bán ra theo từng hạng vé</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="16" t="inlineStr">
         <is>
           <t>Sự kiện có 3 hạng vé</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="16" t="inlineStr">
         <is>
           <t>Mở dashboard thống kê</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="16" t="inlineStr">
         <is>
           <t>1. Quan sát thống kê từng hạng vé</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62" s="16" t="inlineStr">
         <is>
           <t>Hiển thị đúng số lượng vé đã bán và tỷ lệ lấp đầy theo hạng</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J62" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="K62" s="16" t="inlineStr"/>
+      <c r="L62" s="16" t="inlineStr"/>
+      <c r="M62" s="16" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>TC-FR13-003</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="16" t="inlineStr">
         <is>
           <t>FR-13</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="16" t="inlineStr">
         <is>
           <t>Bảng quyết định</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>Đối soát trừ tiền khi có vé bị khách hàng hủy</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="16" t="inlineStr">
         <is>
           <t>Có 1 vé 500.000đ bị hủy trước 48h</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra tổng doanh thu</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="16" t="inlineStr">
         <is>
           <t>1. Xem báo cáo tài chính sự kiện</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" s="16" t="inlineStr">
         <is>
           <t>Doanh thu sự kiện được trừ chính xác phần tiền hoàn lại</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I63" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J63" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+      <c r="K63" s="16" t="inlineStr"/>
+      <c r="L63" s="16" t="inlineStr"/>
+      <c r="M63" s="16" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-001</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="16" t="inlineStr">
         <is>
           <t>FR-14</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="16" t="inlineStr">
         <is>
           <t>Phân hoạch tương đương (EP)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>Khách xem danh sách đơn hàng đã đặt mua thành công</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="16" t="inlineStr">
         <is>
           <t>Đã đăng nhập tài khoản Khách</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="16" t="inlineStr">
         <is>
           <t>Mở /orders</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="16" t="inlineStr">
         <is>
           <t>1. Mở trang Lịch sử đơn hàng</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" s="16" t="inlineStr">
         <is>
           <t>Hiển thị danh sách các đơn hàng gồm mã đơn, ngày mua, tổng tiền</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J64" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+      <c r="K64" s="16" t="inlineStr"/>
+      <c r="L64" s="16" t="inlineStr"/>
+      <c r="M64" s="16" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-002</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="16" t="inlineStr">
         <is>
           <t>FR-14</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="16" t="inlineStr">
         <is>
           <t>Phân hoạch tương đương (EP)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>Xem chi tiết vé điện tử kèm mã QR Code</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="16" t="inlineStr">
         <is>
           <t>Đơn hàng ở trạng thái COMPLETED</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="16" t="inlineStr">
         <is>
           <t>Bấm xem vé</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="16" t="inlineStr">
         <is>
           <t>1. Bấm Xem vé tại đơn hàng hợp lệ</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" s="16" t="inlineStr">
         <is>
           <t>Hiển thị mã QR Code định danh sắc nét và mã vé dạng chuỗi</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J65" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+      <c r="K65" s="16" t="inlineStr"/>
+      <c r="L65" s="16" t="inlineStr"/>
+      <c r="M65" s="16" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-003</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="16" t="inlineStr">
         <is>
           <t>FR-14</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="16" t="inlineStr">
         <is>
           <t>Phân quyền</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="16" t="inlineStr">
         <is>
           <t>Khách A cố tình xem đơn hàng của Khách B qua URL trực tiếp</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập Khách A</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="16" t="inlineStr">
         <is>
           <t>Truy cập /orders/ORDER_OF_USER_B</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="16" t="inlineStr">
         <is>
           <t>1. Nhập ID đơn hàng của người khác lên URL</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" s="16" t="inlineStr">
         <is>
           <t>Bị chặn HTTP 403 Forbidden hoặc trả về 404 Không tìm thấy</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I66" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J66" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+      <c r="K66" s="16" t="inlineStr"/>
+      <c r="L66" s="16" t="inlineStr"/>
+      <c r="M66" s="16" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-004</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="16" t="inlineStr">
         <is>
           <t>FR-14</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="16" t="inlineStr">
         <is>
           <t>Chuyển trạng thái</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra trạng thái đơn hàng khi thanh toán thất bại</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="16" t="inlineStr">
         <is>
           <t>Tạo đơn nhưng hủy thanh toán PayOS</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra đơn hàng</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="16" t="inlineStr">
         <is>
           <t>1. Quan sát trạng thái đơn hàng</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" s="16" t="inlineStr">
         <is>
           <t>Đơn hàng hiển thị trạng thái CANCELLED hoặc PENDING_PAYMENT</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I67" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J67" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="K67" s="16" t="inlineStr"/>
+      <c r="L67" s="16" t="inlineStr"/>
+      <c r="M67" s="16" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="16" t="inlineStr">
         <is>
           <t>TC-FLOW01-001</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="16" t="inlineStr">
         <is>
           <t>FLOW-01</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="16" t="inlineStr">
         <is>
           <t>Use case / E2E</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>E2E: Đặt vé hoàn chỉnh từ Đăng nhập đến Nhận mã vé thành công</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="16" t="inlineStr">
         <is>
           <t>Tài khoản Khách có đủ số dư ví, sự kiện còn vé</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="16" t="inlineStr">
         <is>
           <t>Sự kiện 1, Hạng vé GA, quantity=2, ví nội bộ</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="16" t="inlineStr">
         <is>
           <t>1. Đăng nhập attendee
 2. Mở Sự kiện 1
@@ -5282,170 +5294,170 @@
 5. Hoàn tất đơn</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H68" s="16" t="inlineStr">
         <is>
           <t>Đơn hàng thành công, trừ số dư ví, xuất 2 mã vé điện tử hợp lệ</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I68" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J68" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="K68" s="16" t="inlineStr"/>
+      <c r="L68" s="16" t="inlineStr"/>
+      <c r="M68" s="16" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="16" t="inlineStr">
         <is>
           <t>TC-FLOW01-002</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="16" t="inlineStr">
         <is>
           <t>FLOW-01</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="16" t="inlineStr">
         <is>
           <t>Use case / E2E</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>E2E: Đặt vé thất bại do số dư ví không đủ tiền</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="16" t="inlineStr">
         <is>
           <t>Tài khoản Khách số dư 50.000đ</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="16" t="inlineStr">
         <is>
           <t>Sự kiện 1, vé 300.000đ</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="16" t="inlineStr">
         <is>
           <t>1. Chọn mua vé 300.000đ
 2. Bấm thanh toán ví</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" s="16" t="inlineStr">
         <is>
           <t>Báo lỗi số dư không đủ, không trừ tiền, không tạo vé, đơn ở trạng thái chờ</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I69" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J69" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="K69" s="16" t="inlineStr"/>
+      <c r="L69" s="16" t="inlineStr"/>
+      <c r="M69" s="16" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="16" t="inlineStr">
         <is>
           <t>TC-FLOW01-003</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="16" t="inlineStr">
         <is>
           <t>FLOW-01</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="16" t="inlineStr">
         <is>
           <t>Use case / E2E</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>E2E: Đặt vé áp dụng mã giảm giá và thanh toán thành công</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="16" t="inlineStr">
         <is>
           <t>Khách có mã GIAM50K, ví đủ tiền</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="16" t="inlineStr">
         <is>
           <t>Đơn 500.000đ, voucher GIAM50K</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="16" t="inlineStr">
         <is>
           <t>1. Chọn 2 vé
 2. Nhập voucher GIAM50K
 3. Thanh toán ví</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70" s="16" t="inlineStr">
         <is>
           <t>Khấu trừ đúng 50.000đ, thanh toán 450.000đ, xuất vé thành công</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I70" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J70" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+      <c r="K70" s="16" t="inlineStr"/>
+      <c r="L70" s="16" t="inlineStr"/>
+      <c r="M70" s="16" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="16" t="inlineStr">
         <is>
           <t>TC-FLOW02-001</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="16" t="inlineStr">
         <is>
           <t>FLOW-02</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="16" t="inlineStr">
         <is>
           <t>Use case / E2E</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>E2E: Ban tổ chức tạo sự kiện mới và Admin phê duyệt hiển thị</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="16" t="inlineStr">
         <is>
           <t>Tài khoản BTC và Admin có sẵn</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="16" t="inlineStr">
         <is>
           <t>Sự kiện mới hợp lệ</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="16" t="inlineStr">
         <is>
           <t>1. BTC tạo sự kiện
 2. Gửi duyệt
@@ -5453,792 +5465,370 @@
 4. Khách kiểm tra trang chủ</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H71" s="16" t="inlineStr">
         <is>
           <t>Sự kiện hiển thị công khai trên trang chủ ở trạng thái mở bán</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I71" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J71" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
+      <c r="K71" s="16" t="inlineStr"/>
+      <c r="L71" s="16" t="inlineStr"/>
+      <c r="M71" s="16" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="16" t="inlineStr">
         <is>
           <t>TC-FLOW02-002</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="16" t="inlineStr">
         <is>
           <t>FLOW-02</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="16" t="inlineStr">
         <is>
           <t>Use case / E2E</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>E2E: Admin xem xét và từ chối sự kiện không đạt tiêu chuẩn</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="16" t="inlineStr">
         <is>
           <t>Sự kiện PENDING</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" s="16" t="inlineStr">
         <is>
           <t>Admin từ chối kèm lý do</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" s="16" t="inlineStr">
         <is>
           <t>1. Admin mở danh sách chờ duyệt
 2. Bấm Từ chối sự kiện</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H72" s="16" t="inlineStr">
         <is>
           <t>Sự kiện chuyển REJECTED, không xuất hiện trên trang chủ</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I72" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J72" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="K72" s="16" t="inlineStr"/>
+      <c r="L72" s="16" t="inlineStr"/>
+      <c r="M72" s="16" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="16" t="inlineStr">
         <is>
           <t>TC-FLOW03-001</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="16" t="inlineStr">
         <is>
           <t>FLOW-03</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="16" t="inlineStr">
         <is>
           <t>Use case / E2E</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>E2E: Nhân viên soát vé quét mã và ghi nhận khách vào cổng</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" s="16" t="inlineStr">
         <is>
           <t>Khách đã mua vé hợp lệ</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" s="16" t="inlineStr">
         <is>
           <t>Mã vé của khách</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="16" t="inlineStr">
         <is>
           <t>1. Khách xuất trình vé
 2. Nhân viên quét mã
 3. Xác nhận check-in</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73" s="16" t="inlineStr">
         <is>
           <t>Hệ thống báo hợp lệ màu xanh, ghi nhận mốc giờ vào cổng</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I73" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J73" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
+      <c r="K73" s="16" t="inlineStr"/>
+      <c r="L73" s="16" t="inlineStr"/>
+      <c r="M73" s="16" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="16" t="inlineStr">
         <is>
           <t>TC-FLOW03-002</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="16" t="inlineStr">
         <is>
           <t>FLOW-03</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="16" t="inlineStr">
         <is>
           <t>Use case / E2E</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>E2E: Quét trùng vé tại cổng soát vé phát hiện gian lận</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E74" s="16" t="inlineStr">
         <is>
           <t>Vé đã check-in thành công trước đó</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" s="16" t="inlineStr">
         <is>
           <t>Mã vé đã quét</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" s="16" t="inlineStr">
         <is>
           <t>1. Khách thứ 2 xuất trình vé trùng
 2. Nhân viên quét mã</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H74" s="16" t="inlineStr">
         <is>
           <t>Hệ thống cảnh báo đỏ/vàng: Vé đã được sử dụng, từ chối vào cổng</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I74" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J74" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
+      <c r="K74" s="16" t="inlineStr"/>
+      <c r="L74" s="16" t="inlineStr"/>
+      <c r="M74" s="16" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="16" t="inlineStr">
         <is>
           <t>TC-FLOW03-003</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="16" t="inlineStr">
         <is>
           <t>FLOW-03</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="16" t="inlineStr">
         <is>
           <t>Use case / E2E</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="16" t="inlineStr">
         <is>
           <t>E2E: Xuất báo cáo điểm danh Excel sau khi hoàn tất soát vé</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="16" t="inlineStr">
         <is>
           <t>Sự kiện đã có khách check-in và khách vắng</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="16" t="inlineStr">
         <is>
           <t>Bấm xuất file</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="16" t="inlineStr">
         <is>
           <t>1. BTC mở tab Người tham gia
 2. Bấm Xuất Excel Soát Vé</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75" s="16" t="inlineStr">
         <is>
           <t>File Excel tải về phản ánh đúng trạng thái từng khách</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I75" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J75" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
+      <c r="K75" s="16" t="inlineStr"/>
+      <c r="L75" s="16" t="inlineStr"/>
+      <c r="M75" s="16" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="16" t="inlineStr">
         <is>
           <t>TC-FLOW04-001</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="16" t="inlineStr">
         <is>
           <t>FLOW-04</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="16" t="inlineStr">
         <is>
           <t>Use case / E2E</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>E2E: Khách yêu cầu hủy vé trước 48h và nhận hoàn 90% tiền ví</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E76" s="16" t="inlineStr">
         <is>
           <t>Khách có vé hợp lệ sự kiện diễn ra sau 3 ngày</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" s="16" t="inlineStr">
         <is>
           <t>Thao tác hủy vé</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G76" s="16" t="inlineStr">
         <is>
           <t>1. Khách vào chi tiết vé
 2. Bấm Hủy vé
 3. Xác nhận</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H76" s="16" t="inlineStr">
         <is>
           <t>Vé chuyển CANCELLED, ví khách được cộng lại 90% số tiền vé</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I76" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J76" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
+      <c r="K76" s="16" t="inlineStr"/>
+      <c r="L76" s="16" t="inlineStr"/>
+      <c r="M76" s="16" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="16" t="inlineStr">
         <is>
           <t>TC-FLOW04-002</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="16" t="inlineStr">
         <is>
           <t>FLOW-04</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="16" t="inlineStr">
         <is>
           <t>Use case / E2E</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>E2E: Khách yêu cầu hủy vé sát giờ sự kiện &lt; 24h</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" s="16" t="inlineStr">
         <is>
           <t>Vé của sự kiện bắt đầu sau 5 giờ</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" s="16" t="inlineStr">
         <is>
           <t>Thao tác hủy vé</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" s="16" t="inlineStr">
         <is>
           <t>1. Gửi yêu cầu hủy vé sát giờ sự kiện</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H77" s="16" t="inlineStr">
         <is>
           <t>Hệ thống từ chối hủy vé theo quy định &lt; 24h không được hoàn tiền</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I77" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J77" s="16" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K77" s="16" t="inlineStr">
         <is>
           <t>Hệ thống vẫn chấp nhận hủy vé và hoàn tiền vào ví khách</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="L77" s="16" t="inlineStr">
         <is>
           <t>BUG-003</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
-    </row>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
+      <c r="M77" s="16" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="C5:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn giá trị trong danh sách" type="list" errorStyle="stop" operator="between">
@@ -6266,7 +5856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L499"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.1" customWidth="1" style="16" min="1" max="1"/>
@@ -7358,470 +6948,6 @@
       <c r="K35" s="24" t="n"/>
       <c r="L35" s="24" t="n"/>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="C5:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn giá trị trong danh sách" type="list" errorStyle="stop" operator="between">
@@ -7845,7 +6971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L499"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.9" customWidth="1" style="16" min="1" max="1"/>
@@ -8682,470 +7808,6 @@
       <c r="K35" s="24" t="n"/>
       <c r="L35" s="24" t="n"/>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9159,7 +7821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q499"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11.5" customWidth="1" style="16" min="1" max="1"/>
@@ -10983,470 +9645,6 @@
       <c r="P35" s="24" t="n"/>
       <c r="Q35" s="24" t="n"/>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="C5:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn giá trị trong danh sách" type="list" errorStyle="stop" operator="between">
